--- a/UserData/RegistrationUsers.xlsx
+++ b/UserData/RegistrationUsers.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
       <c r="H4" s="1" t="n"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/UserData/RegistrationUsers.xlsx
+++ b/UserData/RegistrationUsers.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Forget</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
